--- a/transport_tests/transport_data.xlsx
+++ b/transport_tests/transport_data.xlsx
@@ -25659,6 +25659,21 @@
           <t>1</t>
         </is>
       </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>ДЪЛВАН ЕООД</t>
+        </is>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>ИВАН ГЕОРГИЕВ ТУРМАНОВ</t>
+        </is>
+      </c>
+      <c r="H278" t="inlineStr">
+        <is>
+          <t>А7660КР</t>
+        </is>
+      </c>
       <c r="J278" s="2" t="n">
         <v>60</v>
       </c>
@@ -28464,6 +28479,21 @@
           <t>1</t>
         </is>
       </c>
+      <c r="F309" t="inlineStr">
+        <is>
+          <t>ДЪЛВАН ЕООД</t>
+        </is>
+      </c>
+      <c r="G309" t="inlineStr">
+        <is>
+          <t>ИВАН ГЕОРГИЕВ ТУРМАНОВ</t>
+        </is>
+      </c>
+      <c r="H309" t="inlineStr">
+        <is>
+          <t>А7660КР</t>
+        </is>
+      </c>
       <c r="K309" s="2" t="n">
         <v>8000</v>
       </c>
@@ -28507,6 +28537,5618 @@
       <c r="Z309" t="inlineStr">
         <is>
           <t>31</t>
+        </is>
+      </c>
+    </row>
+    <row r="310" ht="19.2" customHeight="1">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>20260908-0001</t>
+        </is>
+      </c>
+      <c r="B310" s="1" t="n">
+        <v>46266</v>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>Русе- Кацелово-Копривец-Островче-Ушинци</t>
+        </is>
+      </c>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F310" t="inlineStr">
+        <is>
+          <t>ЕЛ-ПЛАМ ТРАНС ЕООД</t>
+        </is>
+      </c>
+      <c r="G310" t="inlineStr">
+        <is>
+          <t>ЕЛКО ИВАНОВ</t>
+        </is>
+      </c>
+      <c r="J310" s="2" t="n">
+        <v>237</v>
+      </c>
+      <c r="K310" s="2" t="n">
+        <v>15800</v>
+      </c>
+      <c r="L310" s="2" t="n">
+        <v>403</v>
+      </c>
+      <c r="M310" s="3" t="n">
+        <v>25.50632911392405</v>
+      </c>
+      <c r="O310" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P310" s="2" t="n">
+        <v>3800</v>
+      </c>
+      <c r="T310" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U310" s="4" t="n">
+        <v>46273.73616655092</v>
+      </c>
+      <c r="V310" t="inlineStr">
+        <is>
+          <t>Plamen Svetoslavov</t>
+        </is>
+      </c>
+      <c r="W310" s="4" t="n">
+        <v>46280.51179708333</v>
+      </c>
+      <c r="X310" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y310" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="Z310" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+    </row>
+    <row r="311" ht="19.2" customHeight="1">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>20260908-0002</t>
+        </is>
+      </c>
+      <c r="B311" s="1" t="n">
+        <v>46267</v>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>Русе-Войново-Тервел</t>
+        </is>
+      </c>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t>ЕЛ-ПЛАМ ТРАНС ЕООД</t>
+        </is>
+      </c>
+      <c r="G311" t="inlineStr">
+        <is>
+          <t>ЕЛКО ИВАНОВ</t>
+        </is>
+      </c>
+      <c r="J311" s="2" t="n">
+        <v>170</v>
+      </c>
+      <c r="K311" s="2" t="n">
+        <v>18700</v>
+      </c>
+      <c r="L311" s="2" t="n">
+        <v>289</v>
+      </c>
+      <c r="M311" s="3" t="n">
+        <v>15.45454545454546</v>
+      </c>
+      <c r="O311" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P311" s="2" t="n">
+        <v>18700</v>
+      </c>
+      <c r="T311" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U311" s="4" t="n">
+        <v>46273.74273721065</v>
+      </c>
+      <c r="V311" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W311" s="4" t="n">
+        <v>46273.74463137732</v>
+      </c>
+      <c r="X311" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y311" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="Z311" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+    </row>
+    <row r="312" ht="19.2" customHeight="1">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>20260908-0003</t>
+        </is>
+      </c>
+      <c r="B312" s="1" t="n">
+        <v>46266</v>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>Варна-Лукойл база Аспарухово-Любен-Сенокос-Варна</t>
+        </is>
+      </c>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t>ТРАНС ОЙЛ ЕООД</t>
+        </is>
+      </c>
+      <c r="G312" t="inlineStr">
+        <is>
+          <t>ДИАН СТОЯНОВ АЛЕКСАНДРОВ</t>
+        </is>
+      </c>
+      <c r="H312" t="inlineStr">
+        <is>
+          <t>B7902TM</t>
+        </is>
+      </c>
+      <c r="J312" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="K312" s="2" t="n">
+        <v>18000</v>
+      </c>
+      <c r="L312" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="M312" s="3" t="n">
+        <v>16.66666666666667</v>
+      </c>
+      <c r="O312" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P312" s="2" t="n">
+        <v>18000</v>
+      </c>
+      <c r="T312" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U312" s="4" t="n">
+        <v>46273.74467299769</v>
+      </c>
+      <c r="V312" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W312" s="4" t="n">
+        <v>46273.74582336806</v>
+      </c>
+      <c r="X312" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y312" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="Z312" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+    </row>
+    <row r="313" ht="19.2" customHeight="1">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>20260908-0004</t>
+        </is>
+      </c>
+      <c r="B313" s="1" t="n">
+        <v>46266</v>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>Варна-Аспарухово-Енево-Есеница-Девня-Варна</t>
+        </is>
+      </c>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F313" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G313" t="inlineStr">
+        <is>
+          <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H313" t="inlineStr">
+        <is>
+          <t>CB2201CC</t>
+        </is>
+      </c>
+      <c r="J313" s="2" t="n">
+        <v>250</v>
+      </c>
+      <c r="K313" s="2" t="n">
+        <v>32300</v>
+      </c>
+      <c r="L313" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="M313" s="3" t="n">
+        <v>9.287925696594426</v>
+      </c>
+      <c r="N313" s="2" t="n">
+        <v>14000</v>
+      </c>
+      <c r="O313" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P313" s="2" t="n">
+        <v>32300</v>
+      </c>
+      <c r="T313" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U313" s="4" t="n">
+        <v>46273.745934375</v>
+      </c>
+      <c r="V313" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W313" s="4" t="n">
+        <v>46273.74872</v>
+      </c>
+      <c r="X313" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y313" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="Z313" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+    </row>
+    <row r="314" ht="19.2" customHeight="1">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>20260908-0005</t>
+        </is>
+      </c>
+      <c r="B314" s="1" t="n">
+        <v>46267</v>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>Варна-Аспарухово-Дългопол-Блъсково-Брестак-Нова Камена-Тервел-Черна-Добрич-Брестак-Варна</t>
+        </is>
+      </c>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="F314" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G314" t="inlineStr">
+        <is>
+          <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H314" t="inlineStr">
+        <is>
+          <t>CB2201CC</t>
+        </is>
+      </c>
+      <c r="J314" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="K314" s="2" t="n">
+        <v>35500</v>
+      </c>
+      <c r="L314" s="2" t="n">
+        <v>480</v>
+      </c>
+      <c r="M314" s="3" t="n">
+        <v>13.52112676056338</v>
+      </c>
+      <c r="O314" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P314" s="2" t="n">
+        <v>28500</v>
+      </c>
+      <c r="T314" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U314" s="4" t="n">
+        <v>46273.74878560185</v>
+      </c>
+      <c r="V314" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W314" s="4" t="n">
+        <v>46273.75278450231</v>
+      </c>
+      <c r="X314" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y314" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="Z314" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+    </row>
+    <row r="315" ht="19.2" customHeight="1">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>20260908-0006</t>
+        </is>
+      </c>
+      <c r="B315" s="1" t="n">
+        <v>46268</v>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>НХК-Невестино-Риш-Нова Бяла река-НХК</t>
+        </is>
+      </c>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F315" t="inlineStr">
+        <is>
+          <t>ДИРОСИ ООД</t>
+        </is>
+      </c>
+      <c r="G315" t="inlineStr">
+        <is>
+          <t>СТАНИСЛАВ ДИМИТРОВ ИВАНОВ</t>
+        </is>
+      </c>
+      <c r="H315" t="inlineStr">
+        <is>
+          <t>А1535ВВ</t>
+        </is>
+      </c>
+      <c r="J315" s="2" t="n">
+        <v>130</v>
+      </c>
+      <c r="K315" s="2" t="n">
+        <v>18000</v>
+      </c>
+      <c r="L315" s="2" t="n">
+        <v>208</v>
+      </c>
+      <c r="M315" s="3" t="n">
+        <v>11.55555555555556</v>
+      </c>
+      <c r="O315" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P315" s="2" t="n">
+        <v>18000</v>
+      </c>
+      <c r="T315" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U315" s="4" t="n">
+        <v>46273.75293810185</v>
+      </c>
+      <c r="V315" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W315" s="4" t="n">
+        <v>46273.75581945602</v>
+      </c>
+      <c r="X315" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y315" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="Z315" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+    </row>
+    <row r="316" ht="19.2" customHeight="1">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>20260908-0007</t>
+        </is>
+      </c>
+      <c r="B316" s="1" t="n">
+        <v>46268</v>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>Варна-НХК-Каварна-добрич-Варна</t>
+        </is>
+      </c>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F316" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G316" t="inlineStr">
+        <is>
+          <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H316" t="inlineStr">
+        <is>
+          <t>CB2201CC</t>
+        </is>
+      </c>
+      <c r="J316" s="2" t="n">
+        <v>450</v>
+      </c>
+      <c r="K316" s="2" t="n">
+        <v>33000</v>
+      </c>
+      <c r="L316" s="2" t="n">
+        <v>540</v>
+      </c>
+      <c r="M316" s="3" t="n">
+        <v>16.36363636363636</v>
+      </c>
+      <c r="N316" s="2" t="n">
+        <v>21000</v>
+      </c>
+      <c r="O316" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P316" s="2" t="n">
+        <v>21000</v>
+      </c>
+      <c r="T316" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U316" s="4" t="n">
+        <v>46273.75603104167</v>
+      </c>
+      <c r="V316" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W316" s="4" t="n">
+        <v>46273.75996368055</v>
+      </c>
+      <c r="X316" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y316" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="Z316" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+    </row>
+    <row r="317" ht="19.2" customHeight="1">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>20260908-0008</t>
+        </is>
+      </c>
+      <c r="B317" s="1" t="n">
+        <v>46268</v>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>Аспарухово-Кипра-Вълчи дол-Ботево-Варна-Повеляново-Вълчи дол-Аспарухово</t>
+        </is>
+      </c>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G317" t="inlineStr">
+        <is>
+          <t>ПАВЕЛ СТЕФАНОВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H317" t="inlineStr">
+        <is>
+          <t>Р7826КН</t>
+        </is>
+      </c>
+      <c r="J317" s="2" t="n">
+        <v>305</v>
+      </c>
+      <c r="K317" s="2" t="n">
+        <v>32800</v>
+      </c>
+      <c r="L317" s="2" t="n">
+        <v>366</v>
+      </c>
+      <c r="M317" s="3" t="n">
+        <v>11.15853658536585</v>
+      </c>
+      <c r="O317" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P317" s="2" t="n">
+        <v>32800</v>
+      </c>
+      <c r="T317" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U317" s="4" t="n">
+        <v>46273.76007943287</v>
+      </c>
+      <c r="V317" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W317" s="4" t="n">
+        <v>46273.76287579861</v>
+      </c>
+      <c r="X317" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y317" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="Z317" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+    </row>
+    <row r="318" ht="19.2" customHeight="1">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>20260908-0009</t>
+        </is>
+      </c>
+      <c r="B318" s="1" t="n">
+        <v>46268</v>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>НХК-хотели</t>
+        </is>
+      </c>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t>ДИРОСИ ООД</t>
+        </is>
+      </c>
+      <c r="G318" t="inlineStr">
+        <is>
+          <t>СТАНИСЛАВ ДИМИТРОВ ИВАНОВ</t>
+        </is>
+      </c>
+      <c r="H318" t="inlineStr">
+        <is>
+          <t>А1535ВВ</t>
+        </is>
+      </c>
+      <c r="J318" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="K318" s="2" t="n">
+        <v>3500</v>
+      </c>
+      <c r="L318" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="M318" s="3" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="O318" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="T318" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U318" s="4" t="n">
+        <v>46273.76294291667</v>
+      </c>
+      <c r="V318" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W318" s="4" t="n">
+        <v>46273.76376372685</v>
+      </c>
+      <c r="X318" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y318" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="Z318" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+    </row>
+    <row r="319" ht="19.2" customHeight="1">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>20260908-0010</t>
+        </is>
+      </c>
+      <c r="B319" s="1" t="n">
+        <v>46269</v>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>Хидро</t>
+        </is>
+      </c>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G319" t="inlineStr">
+        <is>
+          <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H319" t="inlineStr">
+        <is>
+          <t>CB2201CC</t>
+        </is>
+      </c>
+      <c r="J319" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="K319" s="2" t="n">
+        <v>32000</v>
+      </c>
+      <c r="L319" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="M319" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="O319" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P319" s="2" t="n">
+        <v>32000</v>
+      </c>
+      <c r="T319" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U319" s="4" t="n">
+        <v>46273.7638015625</v>
+      </c>
+      <c r="V319" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W319" s="4" t="n">
+        <v>46273.76463025463</v>
+      </c>
+      <c r="X319" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y319" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="Z319" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+    </row>
+    <row r="320" ht="19.2" customHeight="1">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>20260908-0011</t>
+        </is>
+      </c>
+      <c r="B320" s="1" t="n">
+        <v>46269</v>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>Варна-Аспарухово-Блъсково-Добрич-Ген. Тошево-Малина-Варна</t>
+        </is>
+      </c>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F320" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G320" t="inlineStr">
+        <is>
+          <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H320" t="inlineStr">
+        <is>
+          <t>CB2201CC</t>
+        </is>
+      </c>
+      <c r="J320" s="2" t="n">
+        <v>320</v>
+      </c>
+      <c r="K320" s="2" t="n">
+        <v>35500</v>
+      </c>
+      <c r="L320" s="2" t="n">
+        <v>384</v>
+      </c>
+      <c r="M320" s="3" t="n">
+        <v>10.8169014084507</v>
+      </c>
+      <c r="O320" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P320" s="2" t="n">
+        <v>22000</v>
+      </c>
+      <c r="T320" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U320" s="4" t="n">
+        <v>46273.76465923611</v>
+      </c>
+      <c r="V320" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W320" s="4" t="n">
+        <v>46273.76665253472</v>
+      </c>
+      <c r="X320" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y320" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="Z320" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+    </row>
+    <row r="321" ht="19.2" customHeight="1">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>20260908-0012</t>
+        </is>
+      </c>
+      <c r="B321" s="1" t="n">
+        <v>46269</v>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>Аспарухово-Добрич-Тервел-Русе</t>
+        </is>
+      </c>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F321" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G321" t="inlineStr">
+        <is>
+          <t>ПАВЕЛ СТЕФАНОВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H321" t="inlineStr">
+        <is>
+          <t>Р7826КН</t>
+        </is>
+      </c>
+      <c r="J321" s="2" t="n">
+        <v>330</v>
+      </c>
+      <c r="K321" s="2" t="n">
+        <v>32500</v>
+      </c>
+      <c r="L321" s="2" t="n">
+        <v>396</v>
+      </c>
+      <c r="M321" s="3" t="n">
+        <v>12.18461538461538</v>
+      </c>
+      <c r="O321" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P321" s="2" t="n">
+        <v>14000</v>
+      </c>
+      <c r="T321" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U321" s="4" t="n">
+        <v>46273.76680313658</v>
+      </c>
+      <c r="V321" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W321" s="4" t="n">
+        <v>46273.76864482639</v>
+      </c>
+      <c r="X321" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y321" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="Z321" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+    </row>
+    <row r="322" ht="19.2" customHeight="1">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>20260908-0013</t>
+        </is>
+      </c>
+      <c r="B322" s="1" t="n">
+        <v>46269</v>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>Русе-Ясеновец-Подайва</t>
+        </is>
+      </c>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t>ЕЛ-ПЛАМ ТРАНС ЕООД</t>
+        </is>
+      </c>
+      <c r="G322" t="inlineStr">
+        <is>
+          <t>ЕЛКО ИВАНОВ</t>
+        </is>
+      </c>
+      <c r="J322" s="2" t="n">
+        <v>119</v>
+      </c>
+      <c r="K322" s="2" t="n">
+        <v>18000</v>
+      </c>
+      <c r="L322" s="2" t="n">
+        <v>203</v>
+      </c>
+      <c r="M322" s="3" t="n">
+        <v>11.27777777777778</v>
+      </c>
+      <c r="O322" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P322" s="2" t="n">
+        <v>18000</v>
+      </c>
+      <c r="T322" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U322" s="4" t="n">
+        <v>46273.76870034722</v>
+      </c>
+      <c r="V322" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W322" s="4" t="n">
+        <v>46273.77029375</v>
+      </c>
+      <c r="X322" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y322" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="Z322" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+    </row>
+    <row r="323" ht="19.2" customHeight="1">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>20260908-0014</t>
+        </is>
+      </c>
+      <c r="B323" s="1" t="n">
+        <v>46273</v>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>Варна-НХК-Долни Чифлик-Девня-Каварна-Варна</t>
+        </is>
+      </c>
+      <c r="E323" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F323" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G323" t="inlineStr">
+        <is>
+          <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H323" t="inlineStr">
+        <is>
+          <t>CB2201CC</t>
+        </is>
+      </c>
+      <c r="J323" s="2" t="n">
+        <v>440</v>
+      </c>
+      <c r="K323" s="2" t="n">
+        <v>32000</v>
+      </c>
+      <c r="L323" s="2" t="n">
+        <v>528</v>
+      </c>
+      <c r="M323" s="3" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="N323" s="2" t="n">
+        <v>21000</v>
+      </c>
+      <c r="O323" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P323" s="2" t="n">
+        <v>32000</v>
+      </c>
+      <c r="T323" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U323" s="4" t="n">
+        <v>46273.77033759259</v>
+      </c>
+      <c r="V323" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W323" s="4" t="n">
+        <v>46273.77268138889</v>
+      </c>
+      <c r="X323" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y323" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="Z323" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+    </row>
+    <row r="324" ht="19.2" customHeight="1">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>20260908-0015</t>
+        </is>
+      </c>
+      <c r="B324" s="1" t="n">
+        <v>46273</v>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>Русе-Близнаци-Доброплодно-Добрич-Паскалево-Аспарухово</t>
+        </is>
+      </c>
+      <c r="E324" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F324" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G324" t="inlineStr">
+        <is>
+          <t>ДАНИЕЛ ПЕНЧЕВ ПЕНЧЕВ</t>
+        </is>
+      </c>
+      <c r="H324" t="inlineStr">
+        <is>
+          <t>Р7826КН</t>
+        </is>
+      </c>
+      <c r="J324" s="2" t="n">
+        <v>390</v>
+      </c>
+      <c r="K324" s="2" t="n">
+        <v>32000</v>
+      </c>
+      <c r="L324" s="2" t="n">
+        <v>468</v>
+      </c>
+      <c r="M324" s="3" t="n">
+        <v>14.625</v>
+      </c>
+      <c r="O324" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P324" s="2" t="n">
+        <v>11300</v>
+      </c>
+      <c r="T324" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U324" s="4" t="n">
+        <v>46273.77272641204</v>
+      </c>
+      <c r="V324" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W324" s="4" t="n">
+        <v>46273.77507295139</v>
+      </c>
+      <c r="X324" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y324" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="Z324" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+    </row>
+    <row r="325" ht="19.2" customHeight="1">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>20260908-0016</t>
+        </is>
+      </c>
+      <c r="B325" s="1" t="n">
+        <v>46274</v>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>Русе-Климент-Тервелл-Карапелит-Русе</t>
+        </is>
+      </c>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F325" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G325" t="inlineStr">
+        <is>
+          <t>ПАВЕЛ СТЕФАНОВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H325" t="inlineStr">
+        <is>
+          <t>Р9581МА</t>
+        </is>
+      </c>
+      <c r="J325" s="2" t="n">
+        <v>380</v>
+      </c>
+      <c r="K325" s="2" t="n">
+        <v>32300</v>
+      </c>
+      <c r="L325" s="2" t="n">
+        <v>456</v>
+      </c>
+      <c r="M325" s="3" t="n">
+        <v>14.11764705882353</v>
+      </c>
+      <c r="O325" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P325" s="2" t="n">
+        <v>32300</v>
+      </c>
+      <c r="T325" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U325" s="4" t="n">
+        <v>46273.77512193287</v>
+      </c>
+      <c r="V325" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W325" s="4" t="n">
+        <v>46273.77716534722</v>
+      </c>
+      <c r="X325" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y325" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="Z325" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+    </row>
+    <row r="326" ht="19.2" customHeight="1">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>20260908-0017</t>
+        </is>
+      </c>
+      <c r="B326" s="1" t="n">
+        <v>46274</v>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>Варна-Аспарухово-Провадия-Енево-Варна</t>
+        </is>
+      </c>
+      <c r="E326" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F326" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G326" t="inlineStr">
+        <is>
+          <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H326" t="inlineStr">
+        <is>
+          <t>CB2201CC</t>
+        </is>
+      </c>
+      <c r="J326" s="2" t="n">
+        <v>210</v>
+      </c>
+      <c r="K326" s="2" t="n">
+        <v>32000</v>
+      </c>
+      <c r="L326" s="2" t="n">
+        <v>252</v>
+      </c>
+      <c r="M326" s="3" t="n">
+        <v>7.875</v>
+      </c>
+      <c r="N326" s="2" t="n">
+        <v>10800</v>
+      </c>
+      <c r="O326" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P326" s="2" t="n">
+        <v>32000</v>
+      </c>
+      <c r="T326" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U326" s="4" t="n">
+        <v>46273.77728480324</v>
+      </c>
+      <c r="V326" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W326" s="4" t="n">
+        <v>46274.68002719907</v>
+      </c>
+      <c r="X326" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y326" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="Z326" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+    </row>
+    <row r="327" ht="19.2" customHeight="1">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>20260908-0018</t>
+        </is>
+      </c>
+      <c r="B327" s="1" t="n">
+        <v>46274</v>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>Варна-Аспарухово-Вълчи дол-Ген.Тошево-Варна</t>
+        </is>
+      </c>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F327" t="inlineStr">
+        <is>
+          <t>ТРАНС ОЙЛ ЕООД</t>
+        </is>
+      </c>
+      <c r="G327" t="inlineStr">
+        <is>
+          <t>ДИАН СТОЯНОВ АЛЕКСАНДРОВ</t>
+        </is>
+      </c>
+      <c r="H327" t="inlineStr">
+        <is>
+          <t>B7902TM</t>
+        </is>
+      </c>
+      <c r="J327" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="K327" s="2" t="n">
+        <v>18000</v>
+      </c>
+      <c r="L327" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="M327" s="3" t="n">
+        <v>16.66666666666667</v>
+      </c>
+      <c r="O327" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P327" s="2" t="n">
+        <v>18000</v>
+      </c>
+      <c r="T327" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U327" s="4" t="n">
+        <v>46273.77942770833</v>
+      </c>
+      <c r="V327" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W327" s="4" t="n">
+        <v>46273.780910625</v>
+      </c>
+      <c r="X327" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y327" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="Z327" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+    </row>
+    <row r="328" ht="19.2" customHeight="1">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>20260909-0001</t>
+        </is>
+      </c>
+      <c r="B328" s="1" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>Аспарухово-Гешаново-Житница-Тервел-Кладенци-Русе</t>
+        </is>
+      </c>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F328" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G328" t="inlineStr">
+        <is>
+          <t>ДАНИЕЛ ПЕНЧЕВ ПЕНЧЕВ</t>
+        </is>
+      </c>
+      <c r="H328" t="inlineStr">
+        <is>
+          <t>Р7826КН</t>
+        </is>
+      </c>
+      <c r="J328" s="2" t="n">
+        <v>340</v>
+      </c>
+      <c r="K328" s="2" t="n">
+        <v>32000</v>
+      </c>
+      <c r="L328" s="2" t="n">
+        <v>408</v>
+      </c>
+      <c r="M328" s="3" t="n">
+        <v>12.75</v>
+      </c>
+      <c r="O328" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P328" s="2" t="n">
+        <v>32000</v>
+      </c>
+      <c r="T328" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U328" s="4" t="n">
+        <v>46274.67245383102</v>
+      </c>
+      <c r="V328" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W328" s="4" t="n">
+        <v>46274.67492622685</v>
+      </c>
+      <c r="X328" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y328" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="Z328" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+    </row>
+    <row r="329" ht="19.2" customHeight="1">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>20260909-0002</t>
+        </is>
+      </c>
+      <c r="B329" s="1" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>Варна-НХК-Каварна-Добрич-Терем-Варна</t>
+        </is>
+      </c>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F329" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G329" t="inlineStr">
+        <is>
+          <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H329" t="inlineStr">
+        <is>
+          <t>CB2201CC</t>
+        </is>
+      </c>
+      <c r="J329" s="2" t="n">
+        <v>490</v>
+      </c>
+      <c r="K329" s="2" t="n">
+        <v>32000</v>
+      </c>
+      <c r="L329" s="2" t="n">
+        <v>504</v>
+      </c>
+      <c r="M329" s="3" t="n">
+        <v>15.75</v>
+      </c>
+      <c r="N329" s="2" t="n">
+        <v>16500</v>
+      </c>
+      <c r="O329" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P329" s="2" t="n">
+        <v>26500</v>
+      </c>
+      <c r="T329" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U329" s="4" t="n">
+        <v>46274.67496945602</v>
+      </c>
+      <c r="V329" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W329" s="4" t="n">
+        <v>46280.74790799768</v>
+      </c>
+      <c r="X329" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y329" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="Z329" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+    </row>
+    <row r="330" ht="19.2" customHeight="1">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>20260914-0001</t>
+        </is>
+      </c>
+      <c r="B330" s="1" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>Русе-Блъсково-Русе</t>
+        </is>
+      </c>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F330" t="inlineStr">
+        <is>
+          <t>ЕЛ-ПЛАМ ТРАНС ЕООД</t>
+        </is>
+      </c>
+      <c r="G330" t="inlineStr">
+        <is>
+          <t>ЕЛКО ИВАНОВ ИВАНОВ</t>
+        </is>
+      </c>
+      <c r="J330" s="2" t="n">
+        <v>165</v>
+      </c>
+      <c r="K330" s="2" t="n">
+        <v>18000</v>
+      </c>
+      <c r="L330" s="2" t="n">
+        <v>281</v>
+      </c>
+      <c r="M330" s="3" t="n">
+        <v>15.61111111111111</v>
+      </c>
+      <c r="O330" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P330" s="2" t="n">
+        <v>18000</v>
+      </c>
+      <c r="T330" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U330" s="4" t="n">
+        <v>46279.71925423611</v>
+      </c>
+      <c r="V330" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W330" s="4" t="n">
+        <v>46279.71998798611</v>
+      </c>
+      <c r="X330" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y330" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="Z330" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+    </row>
+    <row r="331" ht="19.2" customHeight="1">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>20260914-0002</t>
+        </is>
+      </c>
+      <c r="B331" s="1" t="n">
+        <v>46276</v>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>Хидро</t>
+        </is>
+      </c>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F331" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G331" t="inlineStr">
+        <is>
+          <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H331" t="inlineStr">
+        <is>
+          <t>CB2201CC</t>
+        </is>
+      </c>
+      <c r="J331" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="K331" s="2" t="n">
+        <v>30000</v>
+      </c>
+      <c r="L331" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="M331" s="3" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="O331" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P331" s="2" t="n">
+        <v>30000</v>
+      </c>
+      <c r="T331" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U331" s="4" t="n">
+        <v>46279.72021915509</v>
+      </c>
+      <c r="V331" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W331" s="4" t="n">
+        <v>46279.7209178125</v>
+      </c>
+      <c r="X331" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y331" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="Z331" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+    </row>
+    <row r="332" ht="19.2" customHeight="1">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>20260914-0003</t>
+        </is>
+      </c>
+      <c r="B332" s="1" t="n">
+        <v>46276</v>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>АБ + Симо</t>
+        </is>
+      </c>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F332" t="inlineStr">
+        <is>
+          <t>ЗАРА Е</t>
+        </is>
+      </c>
+      <c r="J332" s="2" t="n">
+        <v>110</v>
+      </c>
+      <c r="K332" s="2" t="n">
+        <v>31000</v>
+      </c>
+      <c r="L332" s="2" t="n">
+        <v>143</v>
+      </c>
+      <c r="M332" s="3" t="n">
+        <v>4.612903225806451</v>
+      </c>
+      <c r="O332" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P332" s="2" t="n">
+        <v>27000</v>
+      </c>
+      <c r="T332" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U332" s="4" t="n">
+        <v>46279.72096678241</v>
+      </c>
+      <c r="V332" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W332" s="4" t="n">
+        <v>46279.72161604166</v>
+      </c>
+      <c r="X332" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y332" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="Z332" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+    </row>
+    <row r="333" ht="19.2" customHeight="1">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>20260914-0004</t>
+        </is>
+      </c>
+      <c r="B333" s="1" t="n">
+        <v>46276</v>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>Варна-Аспарухово-Добрич-Варна</t>
+        </is>
+      </c>
+      <c r="E333" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F333" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G333" t="inlineStr">
+        <is>
+          <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H333" t="inlineStr">
+        <is>
+          <t>CB2201CC</t>
+        </is>
+      </c>
+      <c r="J333" s="2" t="n">
+        <v>270</v>
+      </c>
+      <c r="K333" s="2" t="n">
+        <v>32000</v>
+      </c>
+      <c r="L333" s="2" t="n">
+        <v>324</v>
+      </c>
+      <c r="M333" s="3" t="n">
+        <v>10.125</v>
+      </c>
+      <c r="O333" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="T333" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U333" s="4" t="n">
+        <v>46279.72165207176</v>
+      </c>
+      <c r="V333" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W333" s="4" t="n">
+        <v>46279.72348797454</v>
+      </c>
+      <c r="X333" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y333" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="Z333" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+    </row>
+    <row r="334" ht="19.2" customHeight="1">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>20260914-0005</t>
+        </is>
+      </c>
+      <c r="B334" s="1" t="n">
+        <v>46276</v>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>Варна-Аспарухово-Тервел-Варна</t>
+        </is>
+      </c>
+      <c r="E334" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F334" t="inlineStr">
+        <is>
+          <t>ТРАНС ОЙЛ ЕООД</t>
+        </is>
+      </c>
+      <c r="G334" t="inlineStr">
+        <is>
+          <t>ДИАН СТОЯНОВ АЛЕКСАНДРОВ</t>
+        </is>
+      </c>
+      <c r="H334" t="inlineStr">
+        <is>
+          <t>B7902TM</t>
+        </is>
+      </c>
+      <c r="J334" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="K334" s="2" t="n">
+        <v>18000</v>
+      </c>
+      <c r="L334" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="M334" s="3" t="n">
+        <v>16.66666666666667</v>
+      </c>
+      <c r="O334" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P334" s="2" t="n">
+        <v>18000</v>
+      </c>
+      <c r="T334" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U334" s="4" t="n">
+        <v>46279.72353792824</v>
+      </c>
+      <c r="V334" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W334" s="4" t="n">
+        <v>46279.7252112963</v>
+      </c>
+      <c r="X334" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y334" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="Z334" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+    </row>
+    <row r="335" ht="19.2" customHeight="1">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>20260914-0006</t>
+        </is>
+      </c>
+      <c r="B335" s="1" t="n">
+        <v>46277</v>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>НХК-Пчелник-Повеляново-Крумово-Тервел-Русе</t>
+        </is>
+      </c>
+      <c r="E335" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F335" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G335" t="inlineStr">
+        <is>
+          <t>ПАВЕЛ СТЕФАНОВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H335" t="inlineStr">
+        <is>
+          <t>Р9581МА</t>
+        </is>
+      </c>
+      <c r="J335" s="2" t="n">
+        <v>430</v>
+      </c>
+      <c r="K335" s="2" t="n">
+        <v>30000</v>
+      </c>
+      <c r="L335" s="2" t="n">
+        <v>516</v>
+      </c>
+      <c r="M335" s="3" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="O335" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P335" s="2" t="n">
+        <v>23900</v>
+      </c>
+      <c r="T335" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U335" s="4" t="n">
+        <v>46279.72524297453</v>
+      </c>
+      <c r="V335" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W335" s="4" t="n">
+        <v>46279.72751274305</v>
+      </c>
+      <c r="X335" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y335" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="Z335" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+    </row>
+    <row r="336" ht="19.2" customHeight="1">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>20260914-0007</t>
+        </is>
+      </c>
+      <c r="B336" s="1" t="n">
+        <v>46279</v>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>Варна-Аспарухово-Неново-Вълчи дол-Ведрина-Малина-Варна</t>
+        </is>
+      </c>
+      <c r="E336" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F336" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G336" t="inlineStr">
+        <is>
+          <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H336" t="inlineStr">
+        <is>
+          <t>CB2201CC</t>
+        </is>
+      </c>
+      <c r="J336" s="2" t="n">
+        <v>290</v>
+      </c>
+      <c r="K336" s="2" t="n">
+        <v>32000</v>
+      </c>
+      <c r="L336" s="2" t="n">
+        <v>348</v>
+      </c>
+      <c r="M336" s="3" t="n">
+        <v>10.875</v>
+      </c>
+      <c r="N336" s="2" t="n">
+        <v>10000</v>
+      </c>
+      <c r="O336" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P336" s="2" t="n">
+        <v>32000</v>
+      </c>
+      <c r="T336" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U336" s="4" t="n">
+        <v>46279.727575625</v>
+      </c>
+      <c r="V336" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W336" s="4" t="n">
+        <v>46279.72902685186</v>
+      </c>
+      <c r="X336" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y336" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="Z336" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+    </row>
+    <row r="337" ht="19.2" customHeight="1">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>20260914-0008</t>
+        </is>
+      </c>
+      <c r="B337" s="1" t="n">
+        <v>46279</v>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>Варна-Аспарухово-Блъсково-Ботево-Варна</t>
+        </is>
+      </c>
+      <c r="E337" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F337" t="inlineStr">
+        <is>
+          <t>ТРАНС ОЙЛ ЕООД</t>
+        </is>
+      </c>
+      <c r="G337" t="inlineStr">
+        <is>
+          <t>ДИАН СТОЯНОВ АЛЕКСАНДРОВ</t>
+        </is>
+      </c>
+      <c r="H337" t="inlineStr">
+        <is>
+          <t>B7902TM</t>
+        </is>
+      </c>
+      <c r="J337" s="2" t="n">
+        <v>230</v>
+      </c>
+      <c r="K337" s="2" t="n">
+        <v>18000</v>
+      </c>
+      <c r="L337" s="2" t="n">
+        <v>230</v>
+      </c>
+      <c r="M337" s="3" t="n">
+        <v>12.77777777777778</v>
+      </c>
+      <c r="O337" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P337" s="2" t="n">
+        <v>18000</v>
+      </c>
+      <c r="T337" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U337" s="4" t="n">
+        <v>46279.72908048611</v>
+      </c>
+      <c r="V337" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W337" s="4" t="n">
+        <v>46279.72991554398</v>
+      </c>
+      <c r="X337" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y337" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="Z337" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+    </row>
+    <row r="338" ht="19.2" customHeight="1">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>20260914-0009</t>
+        </is>
+      </c>
+      <c r="B338" s="1" t="n">
+        <v>46279</v>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>НХК = Каблешково=Калина</t>
+        </is>
+      </c>
+      <c r="E338" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F338" t="inlineStr">
+        <is>
+          <t>ДИРОСИ ООД</t>
+        </is>
+      </c>
+      <c r="G338" t="inlineStr">
+        <is>
+          <t>СТАНИСЛАВ ДИМИТРОВ ИВАНОВ</t>
+        </is>
+      </c>
+      <c r="H338" t="inlineStr">
+        <is>
+          <t>А5420НХ</t>
+        </is>
+      </c>
+      <c r="J338" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="K338" s="2" t="n">
+        <v>5000</v>
+      </c>
+      <c r="L338" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="M338" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="O338" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P338" s="2" t="n">
+        <v>2000</v>
+      </c>
+      <c r="T338" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U338" s="4" t="n">
+        <v>46279.7299588426</v>
+      </c>
+      <c r="V338" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W338" s="4" t="n">
+        <v>46279.73063444444</v>
+      </c>
+      <c r="X338" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y338" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="Z338" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+    </row>
+    <row r="339" ht="19.2" customHeight="1">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>20260915-0001</t>
+        </is>
+      </c>
+      <c r="B339" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>Варна-НХК-Каварна-Добрич-Варна</t>
+        </is>
+      </c>
+      <c r="E339" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F339" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G339" t="inlineStr">
+        <is>
+          <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H339" t="inlineStr">
+        <is>
+          <t>CB2201CC</t>
+        </is>
+      </c>
+      <c r="J339" s="2" t="n">
+        <v>480</v>
+      </c>
+      <c r="K339" s="2" t="n">
+        <v>33000</v>
+      </c>
+      <c r="L339" s="2" t="n">
+        <v>576</v>
+      </c>
+      <c r="M339" s="3" t="n">
+        <v>17.45454545454546</v>
+      </c>
+      <c r="N339" s="2" t="n">
+        <v>17000</v>
+      </c>
+      <c r="O339" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P339" s="2" t="n">
+        <v>19000</v>
+      </c>
+      <c r="T339" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U339" s="4" t="n">
+        <v>46280.74342678241</v>
+      </c>
+      <c r="V339" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W339" s="4" t="n">
+        <v>46280.74848696759</v>
+      </c>
+      <c r="X339" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y339" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="Z339" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+    </row>
+    <row r="340" ht="19.2" customHeight="1">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>20260915-0002</t>
+        </is>
+      </c>
+      <c r="B340" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>Варна-Аспарухово-Провадия-Повеляново -Варна</t>
+        </is>
+      </c>
+      <c r="E340" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F340" t="inlineStr">
+        <is>
+          <t>"СИ-ТРАНС БЪЛГАРИЯ"  ЕООД</t>
+        </is>
+      </c>
+      <c r="G340" t="inlineStr">
+        <is>
+          <t>Живко Демиров Вълчев</t>
+        </is>
+      </c>
+      <c r="H340" t="inlineStr">
+        <is>
+          <t>В9261РА</t>
+        </is>
+      </c>
+      <c r="J340" s="2" t="n">
+        <v>220</v>
+      </c>
+      <c r="K340" s="2" t="n">
+        <v>30000</v>
+      </c>
+      <c r="L340" s="2" t="n">
+        <v>242</v>
+      </c>
+      <c r="M340" s="3" t="n">
+        <v>8.066666666666666</v>
+      </c>
+      <c r="O340" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P340" s="2" t="n">
+        <v>13000</v>
+      </c>
+      <c r="T340" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U340" s="4" t="n">
+        <v>46280.7485278125</v>
+      </c>
+      <c r="V340" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W340" s="4" t="n">
+        <v>46280.75063892361</v>
+      </c>
+      <c r="X340" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y340" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="Z340" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+    </row>
+    <row r="341" ht="19.2" customHeight="1">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>20260915-0003</t>
+        </is>
+      </c>
+      <c r="B341" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>Аспарухово-Добрич-Варна</t>
+        </is>
+      </c>
+      <c r="E341" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F341" t="inlineStr">
+        <is>
+          <t>"СИ-ТРАНС БЪЛГАРИЯ"  ЕООД</t>
+        </is>
+      </c>
+      <c r="G341" t="inlineStr">
+        <is>
+          <t>Живко Демиров Вълчев</t>
+        </is>
+      </c>
+      <c r="H341" t="inlineStr">
+        <is>
+          <t>В9261РА</t>
+        </is>
+      </c>
+      <c r="J341" s="2" t="n">
+        <v>330</v>
+      </c>
+      <c r="K341" s="2" t="n">
+        <v>30000</v>
+      </c>
+      <c r="L341" s="2" t="n">
+        <v>396</v>
+      </c>
+      <c r="M341" s="3" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="O341" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="T341" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U341" s="4" t="n">
+        <v>46280.75068822916</v>
+      </c>
+      <c r="V341" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W341" s="4" t="n">
+        <v>46280.75167625</v>
+      </c>
+      <c r="X341" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y341" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="Z341" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+    </row>
+    <row r="342" ht="19.2" customHeight="1">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>20260915-0004</t>
+        </is>
+      </c>
+      <c r="B342" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>Варна-Енево-Аспарухово-Доброплодно-Жегларци-Карапелит-Киселово-Калиманци-Варна</t>
+        </is>
+      </c>
+      <c r="E342" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F342" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G342" t="inlineStr">
+        <is>
+          <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H342" t="inlineStr">
+        <is>
+          <t>CB2201CC</t>
+        </is>
+      </c>
+      <c r="J342" s="2" t="n">
+        <v>350</v>
+      </c>
+      <c r="K342" s="2" t="n">
+        <v>32000</v>
+      </c>
+      <c r="L342" s="2" t="n">
+        <v>420</v>
+      </c>
+      <c r="M342" s="3" t="n">
+        <v>13.125</v>
+      </c>
+      <c r="O342" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P342" s="2" t="n">
+        <v>32000</v>
+      </c>
+      <c r="T342" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U342" s="4" t="n">
+        <v>46280.75182841435</v>
+      </c>
+      <c r="V342" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W342" s="4" t="n">
+        <v>46280.75503144676</v>
+      </c>
+      <c r="X342" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y342" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="Z342" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+    </row>
+    <row r="343" ht="19.2" customHeight="1">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>20260915-0005</t>
+        </is>
+      </c>
+      <c r="B343" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>Русе-Островче-Ушинци-Подайва-Тервел-Русе</t>
+        </is>
+      </c>
+      <c r="E343" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F343" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G343" t="inlineStr">
+        <is>
+          <t>ДАНИЕЛ ПЕНЧЕВ ПЕНЧЕВ</t>
+        </is>
+      </c>
+      <c r="H343" t="inlineStr">
+        <is>
+          <t>Р7826КН</t>
+        </is>
+      </c>
+      <c r="J343" s="2" t="n">
+        <v>370</v>
+      </c>
+      <c r="K343" s="2" t="n">
+        <v>32000</v>
+      </c>
+      <c r="L343" s="2" t="n">
+        <v>444</v>
+      </c>
+      <c r="M343" s="3" t="n">
+        <v>13.875</v>
+      </c>
+      <c r="O343" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P343" s="2" t="n">
+        <v>32000</v>
+      </c>
+      <c r="T343" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U343" s="4" t="n">
+        <v>46280.75511171296</v>
+      </c>
+      <c r="V343" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W343" s="4" t="n">
+        <v>46280.75683678241</v>
+      </c>
+      <c r="X343" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y343" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="Z343" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+    </row>
+    <row r="344" ht="19.2" customHeight="1">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>20260923-0001</t>
+        </is>
+      </c>
+      <c r="B344" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>Белфери+109</t>
+        </is>
+      </c>
+      <c r="E344" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F344" t="inlineStr">
+        <is>
+          <t>ТРАНС ОЙЛ ЕООД</t>
+        </is>
+      </c>
+      <c r="G344" t="inlineStr">
+        <is>
+          <t>ДИАН СТОЯНОВ АЛЕКСАНДРОВ</t>
+        </is>
+      </c>
+      <c r="H344" t="inlineStr">
+        <is>
+          <t>B7902TM</t>
+        </is>
+      </c>
+      <c r="J344" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="K344" s="2" t="n">
+        <v>8500</v>
+      </c>
+      <c r="L344" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="M344" s="3" t="n">
+        <v>11.76470588235294</v>
+      </c>
+      <c r="O344" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="T344" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U344" s="4" t="n">
+        <v>46288.71528399306</v>
+      </c>
+      <c r="V344" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W344" s="4" t="n">
+        <v>46288.71591094907</v>
+      </c>
+      <c r="X344" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y344" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="Z344" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+    </row>
+    <row r="345" ht="19.2" customHeight="1">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>20260923-0002</t>
+        </is>
+      </c>
+      <c r="B345" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>НХК-Деветак-Риш-Нова Бяла река</t>
+        </is>
+      </c>
+      <c r="E345" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F345" t="inlineStr">
+        <is>
+          <t>ДИРОСИ ООД</t>
+        </is>
+      </c>
+      <c r="G345" t="inlineStr">
+        <is>
+          <t>СТАНИСЛАВ ДИМИТРОВ ИВАНОВ</t>
+        </is>
+      </c>
+      <c r="H345" t="inlineStr">
+        <is>
+          <t>А5420НХ</t>
+        </is>
+      </c>
+      <c r="J345" s="2" t="n">
+        <v>150</v>
+      </c>
+      <c r="K345" s="2" t="n">
+        <v>18000</v>
+      </c>
+      <c r="L345" s="2" t="n">
+        <v>240</v>
+      </c>
+      <c r="M345" s="3" t="n">
+        <v>13.33333333333333</v>
+      </c>
+      <c r="O345" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P345" s="2" t="n">
+        <v>18000</v>
+      </c>
+      <c r="T345" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U345" s="4" t="n">
+        <v>46288.71627721065</v>
+      </c>
+      <c r="V345" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W345" s="4" t="n">
+        <v>46288.71788559027</v>
+      </c>
+      <c r="X345" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y345" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="Z345" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+    </row>
+    <row r="346" ht="19.2" customHeight="1">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>20260923-0003</t>
+        </is>
+      </c>
+      <c r="B346" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>Варна-НХК-Каварна-Добрич-Терем-Варна</t>
+        </is>
+      </c>
+      <c r="E346" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F346" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G346" t="inlineStr">
+        <is>
+          <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H346" t="inlineStr">
+        <is>
+          <t>CB2201CC</t>
+        </is>
+      </c>
+      <c r="J346" s="2" t="n">
+        <v>480</v>
+      </c>
+      <c r="K346" s="2" t="n">
+        <v>32000</v>
+      </c>
+      <c r="L346" s="2" t="n">
+        <v>576</v>
+      </c>
+      <c r="M346" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="N346" s="2" t="n">
+        <v>14000</v>
+      </c>
+      <c r="O346" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P346" s="2" t="n">
+        <v>21000</v>
+      </c>
+      <c r="T346" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U346" s="4" t="n">
+        <v>46288.71793293981</v>
+      </c>
+      <c r="V346" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W346" s="4" t="n">
+        <v>46288.72087140047</v>
+      </c>
+      <c r="X346" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y346" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="Z346" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+    </row>
+    <row r="347" ht="19.2" customHeight="1">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>20260923-0004</t>
+        </is>
+      </c>
+      <c r="B347" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>Варна-Любен-Крумово-Сенокос-Варна</t>
+        </is>
+      </c>
+      <c r="E347" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F347" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G347" t="inlineStr">
+        <is>
+          <t>ГЕОРГИ ИВАНОВ СТОЯНОВ</t>
+        </is>
+      </c>
+      <c r="H347" t="inlineStr">
+        <is>
+          <t>CB2201CC</t>
+        </is>
+      </c>
+      <c r="J347" s="2" t="n">
+        <v>150</v>
+      </c>
+      <c r="K347" s="2" t="n">
+        <v>32500</v>
+      </c>
+      <c r="L347" s="2" t="n">
+        <v>180</v>
+      </c>
+      <c r="M347" s="3" t="n">
+        <v>5.538461538461538</v>
+      </c>
+      <c r="O347" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P347" s="2" t="n">
+        <v>32500</v>
+      </c>
+      <c r="T347" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U347" s="4" t="n">
+        <v>46288.72108383102</v>
+      </c>
+      <c r="V347" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W347" s="4" t="n">
+        <v>46288.7232521875</v>
+      </c>
+      <c r="X347" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y347" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="Z347" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+    </row>
+    <row r="348" ht="19.2" customHeight="1">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>20260923-0005</t>
+        </is>
+      </c>
+      <c r="B348" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>НХК-МП Ленд</t>
+        </is>
+      </c>
+      <c r="E348" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F348" t="inlineStr">
+        <is>
+          <t>ДИРОСИ ООД</t>
+        </is>
+      </c>
+      <c r="G348" t="inlineStr">
+        <is>
+          <t>СТАНИСЛАВ ДИМИТРОВ ИВАНОВ</t>
+        </is>
+      </c>
+      <c r="H348" t="inlineStr">
+        <is>
+          <t>А5420НХ</t>
+        </is>
+      </c>
+      <c r="J348" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="K348" s="2" t="n">
+        <v>6000</v>
+      </c>
+      <c r="L348" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="M348" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="O348" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P348" s="2" t="n">
+        <v>6000</v>
+      </c>
+      <c r="T348" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U348" s="4" t="n">
+        <v>46288.72336778935</v>
+      </c>
+      <c r="V348" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W348" s="4" t="n">
+        <v>46288.72431109954</v>
+      </c>
+      <c r="X348" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y348" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="Z348" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+    </row>
+    <row r="349" ht="19.2" customHeight="1">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>20260923-0006</t>
+        </is>
+      </c>
+      <c r="B349" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>Варна-Аспарухово-Добрич-Варна</t>
+        </is>
+      </c>
+      <c r="E349" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F349" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G349" t="inlineStr">
+        <is>
+          <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H349" t="inlineStr">
+        <is>
+          <t>CB2201CC</t>
+        </is>
+      </c>
+      <c r="J349" s="2" t="n">
+        <v>260</v>
+      </c>
+      <c r="K349" s="2" t="n">
+        <v>36200</v>
+      </c>
+      <c r="L349" s="2" t="n">
+        <v>312</v>
+      </c>
+      <c r="M349" s="3" t="n">
+        <v>8.618784530386741</v>
+      </c>
+      <c r="N349" s="2" t="n">
+        <v>14000</v>
+      </c>
+      <c r="O349" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P349" s="2" t="n">
+        <v>14000</v>
+      </c>
+      <c r="T349" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U349" s="4" t="n">
+        <v>46288.72434427083</v>
+      </c>
+      <c r="V349" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W349" s="4" t="n">
+        <v>46288.72624538194</v>
+      </c>
+      <c r="X349" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y349" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="Z349" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+    </row>
+    <row r="350" ht="19.2" customHeight="1">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>20260923-0007</t>
+        </is>
+      </c>
+      <c r="B350" s="1" t="n">
+        <v>46286</v>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>Курс Живко</t>
+        </is>
+      </c>
+      <c r="E350" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F350" t="inlineStr">
+        <is>
+          <t>"СИ-ТРАНС БЪЛГАРИЯ"  ЕООД</t>
+        </is>
+      </c>
+      <c r="G350" t="inlineStr">
+        <is>
+          <t>Живко Демиров Вълчев</t>
+        </is>
+      </c>
+      <c r="H350" t="inlineStr">
+        <is>
+          <t>В9261РА</t>
+        </is>
+      </c>
+      <c r="J350" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="K350" s="2" t="n">
+        <v>3400</v>
+      </c>
+      <c r="L350" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="M350" s="3" t="n">
+        <v>17.64705882352941</v>
+      </c>
+      <c r="O350" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P350" s="2" t="n">
+        <v>3400</v>
+      </c>
+      <c r="T350" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U350" s="4" t="n">
+        <v>46288.72628569444</v>
+      </c>
+      <c r="V350" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W350" s="4" t="n">
+        <v>46288.72732057871</v>
+      </c>
+      <c r="X350" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y350" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="Z350" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+    </row>
+    <row r="351" ht="19.2" customHeight="1">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>20260923-0008</t>
+        </is>
+      </c>
+      <c r="B351" s="1" t="n">
+        <v>46286</v>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>Варна-НХК-Каварна-Любен-Варна</t>
+        </is>
+      </c>
+      <c r="E351" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F351" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G351" t="inlineStr">
+        <is>
+          <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H351" t="inlineStr">
+        <is>
+          <t>CB2201CC</t>
+        </is>
+      </c>
+      <c r="J351" s="2" t="n">
+        <v>450</v>
+      </c>
+      <c r="K351" s="2" t="n">
+        <v>32000</v>
+      </c>
+      <c r="L351" s="2" t="n">
+        <v>540</v>
+      </c>
+      <c r="M351" s="3" t="n">
+        <v>16.875</v>
+      </c>
+      <c r="N351" s="2" t="n">
+        <v>20000</v>
+      </c>
+      <c r="O351" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P351" s="2" t="n">
+        <v>22000</v>
+      </c>
+      <c r="T351" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U351" s="4" t="n">
+        <v>46288.72735028935</v>
+      </c>
+      <c r="V351" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W351" s="4" t="n">
+        <v>46288.72883091436</v>
+      </c>
+      <c r="X351" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y351" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="Z351" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+    </row>
+    <row r="352" ht="19.2" customHeight="1">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>20260923-0009</t>
+        </is>
+      </c>
+      <c r="B352" s="1" t="n">
+        <v>46286</v>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>Русе-Бяла-Копривец-Ушинци-Вълчи дол - Брестак - Добрич-Нова Камена - Северняк-Русе</t>
+        </is>
+      </c>
+      <c r="E352" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F352" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G352" t="inlineStr">
+        <is>
+          <t>ДАНИЕЛ ПЕНЧЕВ ПЕНЧЕВ</t>
+        </is>
+      </c>
+      <c r="H352" t="inlineStr">
+        <is>
+          <t>Р7826КН</t>
+        </is>
+      </c>
+      <c r="J352" s="2" t="n">
+        <v>620</v>
+      </c>
+      <c r="K352" s="2" t="n">
+        <v>31800</v>
+      </c>
+      <c r="L352" s="2" t="n">
+        <v>744</v>
+      </c>
+      <c r="M352" s="3" t="n">
+        <v>23.39622641509434</v>
+      </c>
+      <c r="O352" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P352" s="2" t="n">
+        <v>13500</v>
+      </c>
+      <c r="T352" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U352" s="4" t="n">
+        <v>46288.72886894676</v>
+      </c>
+      <c r="V352" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W352" s="4" t="n">
+        <v>46288.73306398148</v>
+      </c>
+      <c r="X352" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y352" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="Z352" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+    </row>
+    <row r="353" ht="19.2" customHeight="1">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>20260923-0010</t>
+        </is>
+      </c>
+      <c r="B353" s="1" t="n">
+        <v>46287</v>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>Варна-Аспарухово-Дългопол-Долни Чифлик - Ген Тошево-Добрич-Паскалево-Тервел-Русе</t>
+        </is>
+      </c>
+      <c r="E353" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F353" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G353" t="inlineStr">
+        <is>
+          <t>ПАВЕЛ СТЕФАНОВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H353" t="inlineStr">
+        <is>
+          <t>CB2201CC</t>
+        </is>
+      </c>
+      <c r="J353" s="2" t="n">
+        <v>480</v>
+      </c>
+      <c r="K353" s="2" t="n">
+        <v>37000</v>
+      </c>
+      <c r="L353" s="2" t="n">
+        <v>576</v>
+      </c>
+      <c r="M353" s="3" t="n">
+        <v>15.56756756756757</v>
+      </c>
+      <c r="O353" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P353" s="2" t="n">
+        <v>37000</v>
+      </c>
+      <c r="T353" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U353" s="4" t="n">
+        <v>46288.73310393518</v>
+      </c>
+      <c r="V353" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W353" s="4" t="n">
+        <v>46288.74181456018</v>
+      </c>
+      <c r="X353" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y353" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="Z353" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+    </row>
+    <row r="354" ht="19.2" customHeight="1">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>20260923-0011</t>
+        </is>
+      </c>
+      <c r="B354" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>Хидро+Мелница</t>
+        </is>
+      </c>
+      <c r="E354" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F354" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G354" t="inlineStr">
+        <is>
+          <t>ДАНИЕЛ ПЕНЧЕВ ПЕНЧЕВ</t>
+        </is>
+      </c>
+      <c r="H354" t="inlineStr">
+        <is>
+          <t>Р7826КН</t>
+        </is>
+      </c>
+      <c r="J354" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="K354" s="2" t="n">
+        <v>32000</v>
+      </c>
+      <c r="L354" s="2" t="n">
+        <v>240</v>
+      </c>
+      <c r="M354" s="3" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="O354" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P354" s="2" t="n">
+        <v>35000</v>
+      </c>
+      <c r="T354" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U354" s="4" t="n">
+        <v>46288.7457681713</v>
+      </c>
+      <c r="V354" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W354" s="4" t="n">
+        <v>46288.74732299768</v>
+      </c>
+      <c r="X354" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y354" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="Z354" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+    </row>
+    <row r="355" ht="19.2" customHeight="1">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>20260923-0012</t>
+        </is>
+      </c>
+      <c r="B355" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>Летище Бургас</t>
+        </is>
+      </c>
+      <c r="E355" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F355" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G355" t="inlineStr">
+        <is>
+          <t>ДАНИЕЛ ПЕНЧЕВ ПЕНЧЕВ</t>
+        </is>
+      </c>
+      <c r="H355" t="inlineStr">
+        <is>
+          <t>Р7826КН</t>
+        </is>
+      </c>
+      <c r="J355" s="2" t="n">
+        <v>340</v>
+      </c>
+      <c r="K355" s="2" t="n">
+        <v>20000</v>
+      </c>
+      <c r="L355" s="2" t="n">
+        <v>408</v>
+      </c>
+      <c r="M355" s="3" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="O355" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="T355" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U355" s="4" t="n">
+        <v>46288.74707045139</v>
+      </c>
+      <c r="V355" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W355" s="4" t="n">
+        <v>46288.74789638889</v>
+      </c>
+      <c r="X355" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y355" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="Z355" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+    </row>
+    <row r="356" ht="19.2" customHeight="1">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>20260923-0013</t>
+        </is>
+      </c>
+      <c r="B356" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>НХК-Добрич-Тервел-Русе</t>
+        </is>
+      </c>
+      <c r="E356" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="F356" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G356" t="inlineStr">
+        <is>
+          <t>ДАНИЕЛ ПЕНЧЕВ ПЕНЧЕВ</t>
+        </is>
+      </c>
+      <c r="H356" t="inlineStr">
+        <is>
+          <t>Р7826КН</t>
+        </is>
+      </c>
+      <c r="J356" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="K356" s="2" t="n">
+        <v>32000</v>
+      </c>
+      <c r="L356" s="2" t="n">
+        <v>480</v>
+      </c>
+      <c r="M356" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="O356" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P356" s="2" t="n">
+        <v>20600</v>
+      </c>
+      <c r="T356" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U356" s="4" t="n">
+        <v>46288.74799921297</v>
+      </c>
+      <c r="V356" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W356" s="4" t="n">
+        <v>46288.75425887731</v>
+      </c>
+      <c r="X356" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y356" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="Z356" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+    </row>
+    <row r="357" ht="19.2" customHeight="1">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>20260923-0014</t>
+        </is>
+      </c>
+      <c r="B357" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>Варна - Бяла- Енево - Вълчи дол - Варна</t>
+        </is>
+      </c>
+      <c r="E357" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F357" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G357" t="inlineStr">
+        <is>
+          <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H357" t="inlineStr">
+        <is>
+          <t>Р9581МА</t>
+        </is>
+      </c>
+      <c r="J357" s="2" t="n">
+        <v>440</v>
+      </c>
+      <c r="K357" s="2" t="n">
+        <v>32000</v>
+      </c>
+      <c r="L357" s="2" t="n">
+        <v>528</v>
+      </c>
+      <c r="M357" s="3" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="O357" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P357" s="2" t="n">
+        <v>32000</v>
+      </c>
+      <c r="T357" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U357" s="4" t="n">
+        <v>46288.75532431713</v>
+      </c>
+      <c r="V357" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W357" s="4" t="n">
+        <v>46288.76314701389</v>
+      </c>
+      <c r="X357" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y357" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="Z357" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+    </row>
+    <row r="358" ht="19.2" customHeight="1">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>20260923-0015</t>
+        </is>
+      </c>
+      <c r="B358" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>Варна-Бяла-Варна-Каварна-Добрич-Варна</t>
+        </is>
+      </c>
+      <c r="E358" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F358" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G358" t="inlineStr">
+        <is>
+          <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H358" t="inlineStr">
+        <is>
+          <t>Р9581МА</t>
+        </is>
+      </c>
+      <c r="J358" s="2" t="n">
+        <v>570</v>
+      </c>
+      <c r="K358" s="2" t="n">
+        <v>30000</v>
+      </c>
+      <c r="L358" s="2" t="n">
+        <v>684</v>
+      </c>
+      <c r="M358" s="3" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="N358" s="2" t="n">
+        <v>8000</v>
+      </c>
+      <c r="O358" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P358" s="2" t="n">
+        <v>21000</v>
+      </c>
+      <c r="T358" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U358" s="4" t="n">
+        <v>46288.76320226852</v>
+      </c>
+      <c r="V358" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W358" s="4" t="n">
+        <v>46288.76549767361</v>
+      </c>
+      <c r="X358" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y358" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="Z358" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+    </row>
+    <row r="359" ht="19.2" customHeight="1">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>20260923-0016</t>
+        </is>
+      </c>
+      <c r="B359" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>Хидро - Пещерна</t>
+        </is>
+      </c>
+      <c r="E359" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F359" t="inlineStr">
+        <is>
+          <t>ГРАНД  ПЕТРОЛ ЕООД</t>
+        </is>
+      </c>
+      <c r="J359" s="2" t="n">
+        <v>240</v>
+      </c>
+      <c r="K359" s="2" t="n">
+        <v>20000</v>
+      </c>
+      <c r="L359" s="2" t="n">
+        <v>312</v>
+      </c>
+      <c r="M359" s="3" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="O359" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P359" s="2" t="n">
+        <v>20000</v>
+      </c>
+      <c r="T359" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U359" s="4" t="n">
+        <v>46288.76553940972</v>
+      </c>
+      <c r="V359" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W359" s="4" t="n">
+        <v>46288.76698381944</v>
+      </c>
+      <c r="X359" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y359" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="Z359" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+    </row>
+    <row r="360" ht="19.2" customHeight="1">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>20260928-0001</t>
+        </is>
+      </c>
+      <c r="B360" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>Бяла-Стражица-Бяла</t>
+        </is>
+      </c>
+      <c r="E360" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F360" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G360" t="inlineStr">
+        <is>
+          <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H360" t="inlineStr">
+        <is>
+          <t>Р9581МА</t>
+        </is>
+      </c>
+      <c r="J360" s="2" t="n">
+        <v>150</v>
+      </c>
+      <c r="K360" s="2" t="n">
+        <v>24000</v>
+      </c>
+      <c r="L360" s="2" t="n">
+        <v>180</v>
+      </c>
+      <c r="M360" s="3" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="O360" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="T360" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U360" s="4" t="n">
+        <v>46293.69814486111</v>
+      </c>
+      <c r="V360" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W360" s="4" t="n">
+        <v>46293.701139375</v>
+      </c>
+      <c r="X360" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y360" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="Z360" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+    </row>
+    <row r="361" ht="19.2" customHeight="1">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>20260928-0002</t>
+        </is>
+      </c>
+      <c r="B361" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>Варна-Бяла-Карапелит-Добрич-Варна</t>
+        </is>
+      </c>
+      <c r="E361" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F361" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G361" t="inlineStr">
+        <is>
+          <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H361" t="inlineStr">
+        <is>
+          <t>Р9581МА</t>
+        </is>
+      </c>
+      <c r="J361" s="2" t="n">
+        <v>450</v>
+      </c>
+      <c r="K361" s="2" t="n">
+        <v>30000</v>
+      </c>
+      <c r="L361" s="2" t="n">
+        <v>540</v>
+      </c>
+      <c r="M361" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="O361" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P361" s="2" t="n">
+        <v>7500</v>
+      </c>
+      <c r="T361" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U361" s="4" t="n">
+        <v>46293.7012192824</v>
+      </c>
+      <c r="V361" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W361" s="4" t="n">
+        <v>46293.70243686342</v>
+      </c>
+      <c r="X361" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y361" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="Z361" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+    </row>
+    <row r="362" ht="19.2" customHeight="1">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>20260928-0003</t>
+        </is>
+      </c>
+      <c r="B362" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>Автомагистрали София
+​</t>
+        </is>
+      </c>
+      <c r="E362" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F362" t="inlineStr">
+        <is>
+          <t>ГРАНД  ПЕТРОЛ ЕООД</t>
+        </is>
+      </c>
+      <c r="J362" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="K362" s="2" t="n">
+        <v>20000</v>
+      </c>
+      <c r="L362" s="2" t="n">
+        <v>360</v>
+      </c>
+      <c r="M362" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="O362" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P362" s="2" t="n">
+        <v>20000</v>
+      </c>
+      <c r="T362" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U362" s="4" t="n">
+        <v>46293.7024746875</v>
+      </c>
+      <c r="V362" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W362" s="4" t="n">
+        <v>46293.70352870371</v>
+      </c>
+      <c r="X362" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y362" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="Z362" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+    </row>
+    <row r="363" ht="19.2" customHeight="1">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>20260928-0004</t>
+        </is>
+      </c>
+      <c r="B363" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>Варна-Ботево-Стожер-Ген Колево- Варна</t>
+        </is>
+      </c>
+      <c r="E363" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F363" t="inlineStr">
+        <is>
+          <t>ТРАНС ОЙЛ ЕООД</t>
+        </is>
+      </c>
+      <c r="G363" t="inlineStr">
+        <is>
+          <t>ДИАН СТОЯНОВ АЛЕКСАНДРОВ</t>
+        </is>
+      </c>
+      <c r="J363" s="2" t="n">
+        <v>150</v>
+      </c>
+      <c r="K363" s="2" t="n">
+        <v>13000</v>
+      </c>
+      <c r="L363" s="2" t="n">
+        <v>150</v>
+      </c>
+      <c r="M363" s="3" t="n">
+        <v>11.53846153846154</v>
+      </c>
+      <c r="O363" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P363" s="2" t="n">
+        <v>7000</v>
+      </c>
+      <c r="T363" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U363" s="4" t="n">
+        <v>46293.70356755787</v>
+      </c>
+      <c r="V363" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W363" s="4" t="n">
+        <v>46293.70472444445</v>
+      </c>
+      <c r="X363" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y363" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="Z363" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+    </row>
+    <row r="364" ht="19.2" customHeight="1">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>20260928-0005</t>
+        </is>
+      </c>
+      <c r="B364" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>Варна-НХК-Пчелник-Каварна-Варна</t>
+        </is>
+      </c>
+      <c r="E364" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F364" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G364" t="inlineStr">
+        <is>
+          <t>ГЕОРГИ ИВАНОВ СТОЯНОВ</t>
+        </is>
+      </c>
+      <c r="H364" t="inlineStr">
+        <is>
+          <t>Р9581МА</t>
+        </is>
+      </c>
+      <c r="J364" s="2" t="n">
+        <v>450</v>
+      </c>
+      <c r="K364" s="2" t="n">
+        <v>30000</v>
+      </c>
+      <c r="L364" s="2" t="n">
+        <v>540</v>
+      </c>
+      <c r="M364" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="N364" s="2" t="n">
+        <v>15000</v>
+      </c>
+      <c r="O364" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P364" s="2" t="n">
+        <v>15000</v>
+      </c>
+      <c r="T364" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U364" s="4" t="n">
+        <v>46293.70476439815</v>
+      </c>
+      <c r="V364" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W364" s="4" t="n">
+        <v>46293.7065990625</v>
+      </c>
+      <c r="X364" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y364" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="Z364" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+    </row>
+    <row r="365" ht="19.2" customHeight="1">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>20260928-0006</t>
+        </is>
+      </c>
+      <c r="B365" s="1" t="n">
+        <v>46293</v>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>Русе-Тервел-Русе</t>
+        </is>
+      </c>
+      <c r="E365" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F365" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G365" t="inlineStr">
+        <is>
+          <t>ДАНИЕЛ ПЕНЧЕВ ПЕНЧЕВ</t>
+        </is>
+      </c>
+      <c r="H365" t="inlineStr">
+        <is>
+          <t>Р7826КН</t>
+        </is>
+      </c>
+      <c r="J365" s="2" t="n">
+        <v>330</v>
+      </c>
+      <c r="K365" s="2" t="n">
+        <v>32000</v>
+      </c>
+      <c r="L365" s="2" t="n">
+        <v>396</v>
+      </c>
+      <c r="M365" s="3" t="n">
+        <v>12.375</v>
+      </c>
+      <c r="O365" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P365" s="2" t="n">
+        <v>31000</v>
+      </c>
+      <c r="T365" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U365" s="4" t="n">
+        <v>46293.70663484954</v>
+      </c>
+      <c r="V365" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W365" s="4" t="n">
+        <v>46293.70785103009</v>
+      </c>
+      <c r="X365" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y365" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="Z365" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+    </row>
+    <row r="366" ht="19.2" customHeight="1">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>20260928-0007</t>
+        </is>
+      </c>
+      <c r="B366" s="1" t="n">
+        <v>46293</v>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>Варна-Бяла-Варна</t>
+        </is>
+      </c>
+      <c r="E366" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F366" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G366" t="inlineStr">
+        <is>
+          <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H366" t="inlineStr">
+        <is>
+          <t>Р9581МА</t>
+        </is>
+      </c>
+      <c r="J366" s="2" t="n">
+        <v>420</v>
+      </c>
+      <c r="K366" s="2" t="n">
+        <v>30000</v>
+      </c>
+      <c r="L366" s="2" t="n">
+        <v>504</v>
+      </c>
+      <c r="M366" s="3" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="N366" s="2" t="n">
+        <v>10000</v>
+      </c>
+      <c r="O366" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P366" s="2" t="n">
+        <v>32000</v>
+      </c>
+      <c r="T366" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U366" s="4" t="n">
+        <v>46293.70789803241</v>
+      </c>
+      <c r="V366" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W366" s="4" t="n">
+        <v>46293.70990542824</v>
+      </c>
+      <c r="X366" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y366" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="Z366" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+    </row>
+    <row r="367" ht="19.2" customHeight="1">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>20260928-0008</t>
+        </is>
+      </c>
+      <c r="B367" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>Русе - Житница-Черна-Нова камена-Русе</t>
+        </is>
+      </c>
+      <c r="E367" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F367" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G367" t="inlineStr">
+        <is>
+          <t>ДАНИЕЛ ПЕНЧЕВ ПЕНЧЕВ</t>
+        </is>
+      </c>
+      <c r="H367" t="inlineStr">
+        <is>
+          <t>Р7826КН</t>
+        </is>
+      </c>
+      <c r="J367" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="K367" s="2" t="n">
+        <v>32000</v>
+      </c>
+      <c r="L367" s="2" t="n">
+        <v>480</v>
+      </c>
+      <c r="M367" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="O367" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P367" s="2" t="n">
+        <v>32000</v>
+      </c>
+      <c r="T367" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U367" s="4" t="n">
+        <v>46293.70994758102</v>
+      </c>
+      <c r="V367" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W367" s="4" t="n">
+        <v>46293.71139060185</v>
+      </c>
+      <c r="X367" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y367" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="Z367" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+    </row>
+    <row r="368" ht="19.2" customHeight="1">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>20260928-0009</t>
+        </is>
+      </c>
+      <c r="B368" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>Варна-Аспарухово-Хидро-Варна</t>
+        </is>
+      </c>
+      <c r="E368" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F368" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G368" t="inlineStr">
+        <is>
+          <t>ГЕОРГИ ИВАНОВ СТОЯНОВ</t>
+        </is>
+      </c>
+      <c r="H368" t="inlineStr">
+        <is>
+          <t>CB2201CC</t>
+        </is>
+      </c>
+      <c r="J368" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="K368" s="2" t="n">
+        <v>32000</v>
+      </c>
+      <c r="L368" s="2" t="n">
+        <v>240</v>
+      </c>
+      <c r="M368" s="3" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="O368" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P368" s="2" t="n">
+        <v>32000</v>
+      </c>
+      <c r="T368" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U368" s="4" t="n">
+        <v>46293.71144064815</v>
+      </c>
+      <c r="V368" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W368" s="4" t="n">
+        <v>46296.54406861111</v>
+      </c>
+      <c r="X368" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y368" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="Z368" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+    </row>
+    <row r="369" ht="19.2" customHeight="1">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>20260928-0010</t>
+        </is>
+      </c>
+      <c r="B369" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>Варна-Бяла-Блъсково-Варна</t>
+        </is>
+      </c>
+      <c r="E369" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F369" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G369" t="inlineStr">
+        <is>
+          <t>ГЕОРГИ ИВАНОВ СТОЯНОВ</t>
+        </is>
+      </c>
+      <c r="H369" t="inlineStr">
+        <is>
+          <t>CB2201CC</t>
+        </is>
+      </c>
+      <c r="J369" s="2" t="n">
+        <v>240</v>
+      </c>
+      <c r="K369" s="2" t="n">
+        <v>32000</v>
+      </c>
+      <c r="L369" s="2" t="n">
+        <v>288</v>
+      </c>
+      <c r="M369" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="O369" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P369" s="2" t="n">
+        <v>32000</v>
+      </c>
+      <c r="T369" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U369" s="4" t="n">
+        <v>46293.71249636574</v>
+      </c>
+      <c r="V369" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W369" s="4" t="n">
+        <v>46296.54415320602</v>
+      </c>
+      <c r="X369" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y369" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="Z369" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+    </row>
+    <row r="370" ht="19.2" customHeight="1">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>20260928-0011</t>
+        </is>
+      </c>
+      <c r="B370" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>Ваарна-Аспарухово-Караманите-Добрич-Малина-Варна</t>
+        </is>
+      </c>
+      <c r="E370" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F370" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G370" t="inlineStr">
+        <is>
+          <t>ГЕОРГИ ИЛИЕВ ГЕОРГИЕВ</t>
+        </is>
+      </c>
+      <c r="H370" t="inlineStr">
+        <is>
+          <t>Р9581МА</t>
+        </is>
+      </c>
+      <c r="J370" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="K370" s="2" t="n">
+        <v>30000</v>
+      </c>
+      <c r="L370" s="2" t="n">
+        <v>360</v>
+      </c>
+      <c r="M370" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="O370" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P370" s="2" t="n">
+        <v>9500</v>
+      </c>
+      <c r="T370" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U370" s="4" t="n">
+        <v>46293.7138096875</v>
+      </c>
+      <c r="V370" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W370" s="4" t="n">
+        <v>46293.71562453704</v>
+      </c>
+      <c r="X370" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y370" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="Z370" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+    </row>
+    <row r="371" ht="19.2" customHeight="1">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>20260928-0012</t>
+        </is>
+      </c>
+      <c r="B371" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>ОФИС ВАРНА</t>
+        </is>
+      </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>Варна-НХК-Каварна-Добрич-Варна</t>
+        </is>
+      </c>
+      <c r="E371" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F371" t="inlineStr">
+        <is>
+          <t>ЕВРОУЕЙ СЪРВИЗ ООД</t>
+        </is>
+      </c>
+      <c r="G371" t="inlineStr">
+        <is>
+          <t>ГЕОРГИ ИВАНОВ СТОЯНОВ</t>
+        </is>
+      </c>
+      <c r="H371" t="inlineStr">
+        <is>
+          <t>CB2201CC</t>
+        </is>
+      </c>
+      <c r="J371" s="2" t="n">
+        <v>480</v>
+      </c>
+      <c r="K371" s="2" t="n">
+        <v>32000</v>
+      </c>
+      <c r="L371" s="2" t="n">
+        <v>576</v>
+      </c>
+      <c r="M371" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="N371" s="2" t="n">
+        <v>15000</v>
+      </c>
+      <c r="O371" t="inlineStr">
+        <is>
+          <t>НЕПЛАТЕНА</t>
+        </is>
+      </c>
+      <c r="P371" s="2" t="n">
+        <v>15000</v>
+      </c>
+      <c r="T371" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="U371" s="4" t="n">
+        <v>46293.71581353009</v>
+      </c>
+      <c r="V371" t="inlineStr">
+        <is>
+          <t>Vesela Nikolova</t>
+        </is>
+      </c>
+      <c r="W371" s="4" t="n">
+        <v>46293.71712799768</v>
+      </c>
+      <c r="X371" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y371" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="Z371" t="inlineStr">
+        <is>
+          <t>28</t>
         </is>
       </c>
     </row>
